--- a/output/topology_excel/2550.xlsx
+++ b/output/topology_excel/2550.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,18 +696,18 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,18 +718,18 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,18 +740,18 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F15" t="n">
         <v>14</v>
@@ -770,11 +770,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" t="n">
         <v>18</v>
       </c>
-      <c r="B16" t="n">
-        <v>20</v>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>Door</t>
@@ -784,19 +784,19 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" t="n">
         <v>17</v>
       </c>
-      <c r="B17" t="n">
-        <v>19</v>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>Door</t>
@@ -806,18 +806,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,18 +828,18 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,40 +872,40 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>79</v>
+      </c>
+      <c r="F21" t="n">
         <v>11</v>
-      </c>
-      <c r="B21" t="n">
-        <v>22</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Door</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>80</v>
-      </c>
-      <c r="F21" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B23" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,54 +938,54 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>366</v>
+        <v>79</v>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -993,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>132</v>
+        <v>246</v>
       </c>
       <c r="F26" t="n">
         <v>12</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>382</v>
+        <v>290</v>
       </c>
       <c r="F27" t="n">
         <v>12</v>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F28" t="n">
         <v>12</v>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,18 +1092,18 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="F30" t="n">
-        <v>12</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,18 +1114,18 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="F31" t="n">
-        <v>109</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="F32" t="n">
         <v>145</v>
@@ -1147,7 +1147,7 @@
         <v>4</v>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,18 +1158,18 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>360</v>
+        <v>131</v>
       </c>
       <c r="F33" t="n">
-        <v>145</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>131</v>
+        <v>382</v>
       </c>
       <c r="F34" t="n">
-        <v>113</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
@@ -1191,7 +1191,7 @@
         <v>5</v>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,19 +1202,19 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>132</v>
+        <v>279</v>
       </c>
       <c r="F35" t="n">
-        <v>108</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" t="n">
         <v>6</v>
       </c>
-      <c r="B36" t="n">
-        <v>9</v>
-      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1224,18 +1224,18 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F36" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,18 +1246,18 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>131</v>
+        <v>384</v>
       </c>
       <c r="F37" t="n">
-        <v>111</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B38" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B39" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>281</v>
+        <v>54</v>
       </c>
       <c r="F39" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B40" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,18 +1312,18 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>365</v>
+        <v>231</v>
       </c>
       <c r="F40" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B41" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,18 +1334,18 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>306</v>
+        <v>109</v>
       </c>
       <c r="F41" t="n">
-        <v>271</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B42" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,18 +1356,18 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="F42" t="n">
-        <v>126</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B43" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,18 +1378,18 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="F43" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B44" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>89</v>
+        <v>231</v>
       </c>
       <c r="F44" t="n">
         <v>14</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B45" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,18 +1422,18 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="F45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B46" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,18 +1444,18 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>348</v>
+        <v>133</v>
       </c>
       <c r="F46" t="n">
-        <v>270</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B47" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,15 +1466,15 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F47" t="n">
-        <v>14</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B48" t="n">
         <v>16</v>
@@ -1488,18 +1488,18 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F48" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B49" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="F49" t="n">
         <v>11</v>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B50" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,41 +1532,41 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
+        <v>11</v>
+      </c>
+      <c r="B51" t="n">
+        <v>29</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>115</v>
+      </c>
+      <c r="F51" t="n">
         <v>13</v>
-      </c>
-      <c r="B51" t="n">
-        <v>21</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="n">
-        <v>109</v>
-      </c>
-      <c r="F51" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
+        <v>11</v>
+      </c>
+      <c r="B52" t="n">
         <v>13</v>
       </c>
-      <c r="B52" t="n">
-        <v>22</v>
-      </c>
       <c r="C52" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1576,18 +1576,18 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="F52" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B53" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,18 +1598,18 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="F53" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B54" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,18 +1620,18 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="F54" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B55" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1645,15 +1645,15 @@
         <v>115</v>
       </c>
       <c r="F55" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B56" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,18 +1664,18 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B57" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,18 +1686,18 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="F57" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B58" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1708,18 +1708,18 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F58" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B59" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="F59" t="n">
         <v>38</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B60" t="n">
         <v>19</v>
@@ -1752,18 +1752,18 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F60" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B61" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1774,18 +1774,18 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="F61" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B62" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,18 +1796,18 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="F62" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B63" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1818,18 +1818,18 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="F63" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B64" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1840,18 +1840,18 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="F64" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1862,18 +1862,18 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="F65" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B66" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1884,18 +1884,18 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="F66" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B67" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1909,15 +1909,15 @@
         <v>128</v>
       </c>
       <c r="F67" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B68" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1928,18 +1928,18 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B69" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1950,10 +1950,274 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F69" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>19</v>
+      </c>
+      <c r="B70" t="n">
+        <v>21</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>128</v>
+      </c>
+      <c r="F70" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>20</v>
+      </c>
+      <c r="B71" t="n">
+        <v>22</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>127</v>
+      </c>
+      <c r="F71" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>23</v>
+      </c>
+      <c r="B72" t="n">
+        <v>24</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>121</v>
+      </c>
+      <c r="F72" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>25</v>
+      </c>
+      <c r="B73" t="n">
+        <v>26</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>366</v>
+      </c>
+      <c r="F73" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>27</v>
+      </c>
+      <c r="B74" t="n">
+        <v>28</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>365</v>
+      </c>
+      <c r="F74" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>27</v>
+      </c>
+      <c r="B75" t="n">
+        <v>29</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>133</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>28</v>
+      </c>
+      <c r="B76" t="n">
+        <v>30</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>138</v>
+      </c>
+      <c r="F76" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>29</v>
+      </c>
+      <c r="B77" t="n">
+        <v>30</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>159</v>
+      </c>
+      <c r="F77" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1</v>
+      </c>
+      <c r="B78" t="n">
+        <v>27</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>204</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2</v>
+      </c>
+      <c r="B79" t="n">
+        <v>28</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>204</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>17</v>
+      </c>
+      <c r="B80" t="n">
+        <v>27</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>128</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>18</v>
+      </c>
+      <c r="B81" t="n">
+        <v>28</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>126</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/2550.xlsx
+++ b/output/topology_excel/2550.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>12</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>12</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>14</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>14</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>14</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>14</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>12</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>12</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>12</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>12</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>27</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>27</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>13</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>14</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>11</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>14</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>50</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +899,8 @@
       <c r="F19" t="n">
         <v>45</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +923,8 @@
       <c r="F20" t="n">
         <v>14</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +947,8 @@
       <c r="F21" t="n">
         <v>11</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +971,8 @@
       <c r="F22" t="n">
         <v>12</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +995,8 @@
       <c r="F23" t="n">
         <v>12</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1019,8 @@
       <c r="F24" t="n">
         <v>13</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1043,8 @@
       <c r="F25" t="n">
         <v>11</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1067,8 @@
       <c r="F26" t="n">
         <v>12</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1091,8 @@
       <c r="F27" t="n">
         <v>12</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1115,8 @@
       <c r="F28" t="n">
         <v>12</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1067,13 +1131,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="F29" t="n">
-        <v>109</v>
+        <v>13</v>
+      </c>
+      <c r="G29" t="n">
+        <v>118</v>
+      </c>
+      <c r="H29" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -1089,13 +1159,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>317</v>
+        <v>72</v>
       </c>
       <c r="F30" t="n">
-        <v>145</v>
+        <v>13</v>
+      </c>
+      <c r="G30" t="n">
+        <v>124</v>
+      </c>
+      <c r="H30" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -1119,6 +1195,8 @@
       <c r="F31" t="n">
         <v>12</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1133,13 +1211,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>360</v>
+        <v>71</v>
       </c>
       <c r="F32" t="n">
-        <v>145</v>
+        <v>14</v>
+      </c>
+      <c r="G32" t="n">
+        <v>164</v>
+      </c>
+      <c r="H32" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="33">
@@ -1155,13 +1239,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="F33" t="n">
-        <v>113</v>
+        <v>14</v>
+      </c>
+      <c r="G33" t="n">
+        <v>117</v>
+      </c>
+      <c r="H33" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -1185,6 +1275,8 @@
       <c r="F34" t="n">
         <v>12</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1299,8 @@
       <c r="F35" t="n">
         <v>12</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1323,8 @@
       <c r="F36" t="n">
         <v>27</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1347,8 @@
       <c r="F37" t="n">
         <v>12</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1371,8 @@
       <c r="F38" t="n">
         <v>12</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1287,13 +1387,19 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F39" t="n">
-        <v>40</v>
+        <v>12</v>
+      </c>
+      <c r="G39" t="n">
+        <v>28</v>
+      </c>
+      <c r="H39" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="40">
@@ -1317,6 +1423,8 @@
       <c r="F40" t="n">
         <v>13</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1447,8 @@
       <c r="F41" t="n">
         <v>12</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1471,8 @@
       <c r="F42" t="n">
         <v>12</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1375,13 +1487,19 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F43" t="n">
-        <v>39</v>
+        <v>12</v>
+      </c>
+      <c r="G43" t="n">
+        <v>27</v>
+      </c>
+      <c r="H43" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="44">
@@ -1405,6 +1523,8 @@
       <c r="F44" t="n">
         <v>14</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1547,8 @@
       <c r="F45" t="n">
         <v>13</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1571,8 @@
       <c r="F46" t="n">
         <v>13</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1463,13 +1587,19 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="F47" t="n">
-        <v>108</v>
+        <v>12</v>
+      </c>
+      <c r="G47" t="n">
+        <v>96</v>
+      </c>
+      <c r="H47" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -1485,13 +1615,19 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F48" t="n">
-        <v>111</v>
+        <v>12</v>
+      </c>
+      <c r="G48" t="n">
+        <v>99</v>
+      </c>
+      <c r="H48" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="49">
@@ -1515,6 +1651,8 @@
       <c r="F49" t="n">
         <v>11</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1675,8 @@
       <c r="F50" t="n">
         <v>14</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1699,8 @@
       <c r="F51" t="n">
         <v>13</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +1723,8 @@
       <c r="F52" t="n">
         <v>14</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +1747,8 @@
       <c r="F53" t="n">
         <v>11</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1771,8 @@
       <c r="F54" t="n">
         <v>11</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1645,8 +1793,10 @@
         <v>115</v>
       </c>
       <c r="F55" t="n">
-        <v>17</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1669,6 +1819,8 @@
       <c r="F56" t="n">
         <v>13</v>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1691,6 +1843,8 @@
       <c r="F57" t="n">
         <v>14</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1711,8 +1865,10 @@
         <v>122</v>
       </c>
       <c r="F58" t="n">
-        <v>53</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1733,8 +1889,10 @@
         <v>171</v>
       </c>
       <c r="F59" t="n">
-        <v>38</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +1915,8 @@
       <c r="F60" t="n">
         <v>14</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +1939,8 @@
       <c r="F61" t="n">
         <v>36</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1799,8 +1961,10 @@
         <v>140</v>
       </c>
       <c r="F62" t="n">
-        <v>64</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1823,6 +1987,8 @@
       <c r="F63" t="n">
         <v>11</v>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1845,6 +2011,8 @@
       <c r="F64" t="n">
         <v>11</v>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1867,6 +2035,8 @@
       <c r="F65" t="n">
         <v>36</v>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1889,6 +2059,8 @@
       <c r="F66" t="n">
         <v>12</v>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1911,6 +2083,8 @@
       <c r="F67" t="n">
         <v>12</v>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1933,6 +2107,8 @@
       <c r="F68" t="n">
         <v>12</v>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1955,6 +2131,8 @@
       <c r="F69" t="n">
         <v>13</v>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1977,6 +2155,8 @@
       <c r="F70" t="n">
         <v>14</v>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1999,6 +2179,8 @@
       <c r="F71" t="n">
         <v>11</v>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2021,6 +2203,8 @@
       <c r="F72" t="n">
         <v>13</v>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2043,6 +2227,8 @@
       <c r="F73" t="n">
         <v>27</v>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2065,6 +2251,8 @@
       <c r="F74" t="n">
         <v>28</v>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2087,6 +2275,8 @@
       <c r="F75" t="n">
         <v>13</v>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2109,6 +2299,8 @@
       <c r="F76" t="n">
         <v>14</v>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2131,6 +2323,8 @@
       <c r="F77" t="n">
         <v>38</v>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2153,6 +2347,8 @@
       <c r="F78" t="n">
         <v>1</v>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2175,6 +2371,8 @@
       <c r="F79" t="n">
         <v>1</v>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2197,6 +2395,8 @@
       <c r="F80" t="n">
         <v>1</v>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2219,6 +2419,8 @@
       <c r="F81" t="n">
         <v>1</v>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
